--- a/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
+++ b/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing\system_development\Damascus\V0.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B312951E-B035-4057-83A7-92A5E7141DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DFE409-8230-4049-8970-684E3C5CA9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>Total Cost</t>
   </si>
@@ -111,12 +111,6 @@
   </si>
   <si>
     <t>https://www.xometry.com/</t>
-  </si>
-  <si>
-    <t>FLIR Blackfly Camera</t>
-  </si>
-  <si>
-    <t>Edmunds Optis 25mm Lens</t>
   </si>
   <si>
     <t xml:space="preserve">Seal Glass Ring </t>
@@ -806,17 +800,12 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="A10" s="8"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -826,24 +815,19 @@
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>26</v>
-      </c>
+      <c r="A11" s="8"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="1"/>
       <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -859,7 +843,7 @@
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -875,7 +859,7 @@
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -890,7 +874,7 @@
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -905,7 +889,7 @@
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -918,10 +902,10 @@
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -933,7 +917,7 @@
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -946,7 +930,7 @@
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -959,7 +943,7 @@
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -972,7 +956,7 @@
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -985,7 +969,7 @@
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -998,7 +982,7 @@
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1011,7 +995,7 @@
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1024,7 +1008,7 @@
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1037,7 +1021,7 @@
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1050,7 +1034,7 @@
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1063,7 +1047,7 @@
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1076,7 +1060,7 @@
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -1087,13 +1071,13 @@
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="C30" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -1107,7 +1091,7 @@
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I30" s="4"/>
     </row>

--- a/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
+++ b/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing\system_development\Damascus\V0.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DFE409-8230-4049-8970-684E3C5CA9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA51215D-E13E-4954-9EEF-5E6D119FAD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
   <si>
     <t>Total Cost</t>
   </si>
@@ -131,15 +131,9 @@
     <t>Magnet Sensors</t>
   </si>
   <si>
-    <t>M6x15 Bolt</t>
-  </si>
-  <si>
     <t>M6x20 Bolt</t>
   </si>
   <si>
-    <t>M6 ID 11.8mm OD Washer</t>
-  </si>
-  <si>
     <t>M6 Nut</t>
   </si>
   <si>
@@ -180,6 +174,48 @@
   </si>
   <si>
     <t>https://www.cdwg.com/product/tripp-lite-4-port-industrial-usb-3.0-superspeed-hub-15kv-esd-immunity-metal/3682489?pfm=srh</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Socket-Head-Cap-Screw-M6x1-26WC46</t>
+  </si>
+  <si>
+    <t>Socket Head Cap Screw: M6x1.00 Thread Size, 14 mm Lg, Std, Plain, Stainless Steel, 18-8, 50 PK</t>
+  </si>
+  <si>
+    <t>M6x14 Socket Head Screw</t>
+  </si>
+  <si>
+    <t>M51050.060.0014</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Socket-Head-Cap-Screw-M6x1-26WC48</t>
+  </si>
+  <si>
+    <t>Socket Head Cap Screw: M6x1.00 Thread Size, 20 mm Lg, Std, Plain, Stainless Steel, 18-8, 50 PK</t>
+  </si>
+  <si>
+    <t>M51050.060.0020</t>
+  </si>
+  <si>
+    <t>M6 ID 12mm OD Washer</t>
+  </si>
+  <si>
+    <t>Flat Washer: 18-8, Stainless Steel, M6 Screw Sz, 6.62 mm In Dia, 12 mm Out Dia, 18-8, 50 PK</t>
+  </si>
+  <si>
+    <t>M51420.060.0001</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Flat-Washer-18-8-26WC34</t>
+  </si>
+  <si>
+    <t>M51080.060.0001</t>
+  </si>
+  <si>
+    <t>Hex Nut: Std Hex, M6x1.00 Thread, 10 mm Hex Wd, 5 mm Hex Ht, Stainless Steel, 18-8, Plain, 50 PK</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Hex-Nut-Std-Hex-22YK33</t>
   </si>
 </sst>
 </file>
@@ -791,7 +827,7 @@
         <v>73.290000000000006</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" ref="F9:F15" si="0">D9*E9</f>
+        <f t="shared" ref="F9:F29" si="0">D9*E9</f>
         <v>73.290000000000006</v>
       </c>
       <c r="G9" s="5"/>
@@ -895,7 +931,10 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="F16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G16" s="5"/>
       <c r="H16" s="1"/>
       <c r="I16" s="3"/>
@@ -905,179 +944,259 @@
         <v>30</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="F17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G17" s="5"/>
       <c r="H17" s="1"/>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+        <v>48</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5">
+        <v>4.7</v>
+      </c>
+      <c r="F18" s="5">
+        <f t="shared" si="0"/>
+        <v>4.7</v>
+      </c>
       <c r="G18" s="5"/>
-      <c r="H18" s="1"/>
+      <c r="H18" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+        <v>31</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5">
+        <v>7.58</v>
+      </c>
+      <c r="F19" s="5">
+        <f t="shared" si="0"/>
+        <v>7.58</v>
+      </c>
       <c r="G19" s="5"/>
-      <c r="H19" s="1"/>
+      <c r="H19" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+        <v>53</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5">
+        <v>1.54</v>
+      </c>
+      <c r="F20" s="5">
+        <f t="shared" si="0"/>
+        <v>1.54</v>
+      </c>
       <c r="G20" s="5"/>
-      <c r="H20" s="1"/>
+      <c r="H20" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+        <v>32</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="F21" s="5">
+        <f t="shared" si="0"/>
+        <v>2.95</v>
+      </c>
       <c r="G21" s="5"/>
-      <c r="H21" s="1"/>
+      <c r="H21" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="F22" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G22" s="5"/>
       <c r="H22" s="1"/>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
+      <c r="F23" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G23" s="5"/>
       <c r="H23" s="1"/>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
+      <c r="F24" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G24" s="5"/>
       <c r="H24" s="1"/>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="F25" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G25" s="5"/>
       <c r="H25" s="1"/>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
+      <c r="F26" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G26" s="5"/>
       <c r="H26" s="1"/>
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="F27" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G27" s="5"/>
       <c r="H27" s="1"/>
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="F28" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G28" s="5"/>
       <c r="H28" s="1"/>
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
+      <c r="F29" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G29" s="5"/>
       <c r="H29" s="3"/>
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="C30" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -1091,7 +1210,7 @@
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I30" s="4"/>
     </row>
@@ -1139,7 +1258,7 @@
       </c>
       <c r="F37" s="5">
         <f>SUM(F2:F36)</f>
-        <v>208.69</v>
+        <v>225.46</v>
       </c>
     </row>
   </sheetData>
@@ -1149,8 +1268,12 @@
     <hyperlink ref="H8" r:id="rId2" xr:uid="{0EDC0A57-8E4C-4D3A-8F84-8D905F46C8DF}"/>
     <hyperlink ref="H4" r:id="rId3" xr:uid="{1ECF2406-B0D1-41D2-AB7D-AB233330FD61}"/>
     <hyperlink ref="H30" r:id="rId4" xr:uid="{09C07DD3-BEB0-4324-912F-D9BB7285A77D}"/>
+    <hyperlink ref="H18" r:id="rId5" xr:uid="{626FADE7-D6F2-4623-B41F-525D88835216}"/>
+    <hyperlink ref="H19" r:id="rId6" xr:uid="{E1235693-0AE4-483A-80C1-C4EB98C7CCE2}"/>
+    <hyperlink ref="H20" r:id="rId7" xr:uid="{DFE47E21-CC99-4786-9546-33196C5907C2}"/>
+    <hyperlink ref="H21" r:id="rId8" xr:uid="{B0FFF7C7-7C5F-48BF-B374-ADD953FC535F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
--- a/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
+++ b/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing\system_development\Damascus\V0.5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thienan Hoang\Documents\GitHub\LPBF-Observer\system_development\Damascus\V0.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA51215D-E13E-4954-9EEF-5E6D119FAD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A1DC0E-31C0-4E28-8770-00DFF35A3F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>Total Cost</t>
   </si>
@@ -216,14 +216,27 @@
   </si>
   <si>
     <t>https://www.grainger.com/product/Hex-Nut-Std-Hex-22YK33</t>
+  </si>
+  <si>
+    <t>USB-C to USB-A</t>
+  </si>
+  <si>
+    <t>https://www.cdwg.com/product/tripp-lite-usb-3.0-adapter-converter-usb-a-to-usb-type-c-m-f-usb-c/5238658?pfm=srh</t>
+  </si>
+  <si>
+    <t>Eaton Tripp Lite Series USB 3.0 Adapter Converter USB-A to USB Type C M/F USB-C - USB-C adapter - USB A to 24 pin USB-C</t>
+  </si>
+  <si>
+    <t>U329-000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -292,7 +305,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -317,6 +330,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1215,14 +1229,28 @@
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="5"/>
+      <c r="A31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="10">
+        <v>13.96</v>
+      </c>
+      <c r="F31" s="5">
+        <v>13.96</v>
+      </c>
       <c r="G31" s="5"/>
-      <c r="H31" s="3"/>
+      <c r="H31" s="3" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
@@ -1258,7 +1286,7 @@
       </c>
       <c r="F37" s="5">
         <f>SUM(F2:F36)</f>
-        <v>225.46</v>
+        <v>239.42000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
+++ b/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing\system_development\Damascus\V0.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA51215D-E13E-4954-9EEF-5E6D119FAD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41798B06-F3F8-4A84-B92C-747F8A35EEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
   <si>
     <t>Total Cost</t>
   </si>
@@ -216,14 +216,24 @@
   </si>
   <si>
     <t>https://www.grainger.com/product/Hex-Nut-Std-Hex-22YK33</t>
+  </si>
+  <si>
+    <t>relays</t>
+  </si>
+  <si>
+    <t>RELAY GEN PURPOSE SPST 6A 24V</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/phoenix-contact/2903361/4755334</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -292,7 +302,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -317,6 +327,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -715,10 +729,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="10" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="5"/>
@@ -730,8 +744,8 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
       <c r="G3" s="5"/>
       <c r="H3" s="1"/>
     </row>
@@ -742,8 +756,8 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
       <c r="G4" s="5" t="s">
         <v>15</v>
       </c>
@@ -755,8 +769,8 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
       <c r="G5" s="5"/>
       <c r="H5" s="1"/>
       <c r="I5" s="4"/>
@@ -766,8 +780,8 @@
       <c r="B6" s="2"/>
       <c r="C6" s="4"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
       <c r="G6" s="5"/>
       <c r="H6" s="1"/>
       <c r="I6" s="4"/>
@@ -777,8 +791,8 @@
       <c r="B7" s="2"/>
       <c r="C7" s="4"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
       <c r="G7" s="5"/>
       <c r="H7" s="1"/>
       <c r="I7" s="3"/>
@@ -797,10 +811,10 @@
       <c r="D8" s="2">
         <v>2</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="10">
         <v>12.7</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="10">
         <f>D8*E8</f>
         <v>25.4</v>
       </c>
@@ -823,10 +837,10 @@
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="10">
         <v>73.290000000000006</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="10">
         <f t="shared" ref="F9:F29" si="0">D9*E9</f>
         <v>73.290000000000006</v>
       </c>
@@ -840,8 +854,8 @@
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
       <c r="G10" s="5"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -855,8 +869,8 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
       <c r="G11" s="5"/>
       <c r="H11" s="1"/>
       <c r="I11" s="4"/>
@@ -868,8 +882,8 @@
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5">
+      <c r="E12" s="10"/>
+      <c r="F12" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -884,8 +898,8 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5">
+      <c r="E13" s="10"/>
+      <c r="F13" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -900,8 +914,8 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5">
+      <c r="E14" s="10"/>
+      <c r="F14" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -915,8 +929,8 @@
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5">
+      <c r="E15" s="10"/>
+      <c r="F15" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -930,8 +944,8 @@
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5">
+      <c r="E16" s="10"/>
+      <c r="F16" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -948,8 +962,8 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5">
+      <c r="E17" s="10"/>
+      <c r="F17" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -970,10 +984,10 @@
       <c r="D18" s="2">
         <v>1</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="10">
         <v>4.7</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="10">
         <f t="shared" si="0"/>
         <v>4.7</v>
       </c>
@@ -996,10 +1010,10 @@
       <c r="D19" s="2">
         <v>1</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="10">
         <v>7.58</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="10">
         <f t="shared" si="0"/>
         <v>7.58</v>
       </c>
@@ -1022,10 +1036,10 @@
       <c r="D20" s="2">
         <v>1</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="10">
         <v>1.54</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="10">
         <f t="shared" si="0"/>
         <v>1.54</v>
       </c>
@@ -1048,10 +1062,10 @@
       <c r="D21" s="2">
         <v>1</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="10">
         <v>2.95</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="10">
         <f t="shared" si="0"/>
         <v>2.95</v>
       </c>
@@ -1068,8 +1082,8 @@
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5">
+      <c r="E22" s="10"/>
+      <c r="F22" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1084,8 +1098,8 @@
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5">
+      <c r="E23" s="10"/>
+      <c r="F23" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1100,8 +1114,8 @@
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5">
+      <c r="E24" s="10"/>
+      <c r="F24" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1116,8 +1130,8 @@
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5">
+      <c r="E25" s="10"/>
+      <c r="F25" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1132,8 +1146,8 @@
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5">
+      <c r="E26" s="10"/>
+      <c r="F26" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1148,8 +1162,8 @@
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5">
+      <c r="E27" s="10"/>
+      <c r="F27" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1164,8 +1178,8 @@
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5">
+      <c r="E28" s="10"/>
+      <c r="F28" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1180,7 +1194,8 @@
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="F29" s="5">
+      <c r="E29" s="11"/>
+      <c r="F29" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1201,10 +1216,10 @@
       <c r="D30" s="2">
         <v>1</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="10">
         <v>110</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="10">
         <f>D30*E30</f>
         <v>110</v>
       </c>
@@ -1215,22 +1230,37 @@
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="5"/>
+      <c r="A31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="2">
+        <v>2903361</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+      <c r="E31" s="10">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="F31" s="10">
+        <f>D31*E31</f>
+        <v>18.920000000000002</v>
+      </c>
       <c r="G31" s="5"/>
-      <c r="H31" s="3"/>
+      <c r="H31" s="3" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
       <c r="G32" s="2"/>
       <c r="H32" s="3"/>
     </row>
@@ -1239,18 +1269,26 @@
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
       <c r="G33" s="2"/>
       <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
       <c r="G34" s="2"/>
       <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E37" s="7" t="s">
@@ -1258,7 +1296,7 @@
       </c>
       <c r="F37" s="5">
         <f>SUM(F2:F36)</f>
-        <v>225.46</v>
+        <v>244.38</v>
       </c>
     </row>
   </sheetData>
@@ -1272,8 +1310,9 @@
     <hyperlink ref="H19" r:id="rId6" xr:uid="{E1235693-0AE4-483A-80C1-C4EB98C7CCE2}"/>
     <hyperlink ref="H20" r:id="rId7" xr:uid="{DFE47E21-CC99-4786-9546-33196C5907C2}"/>
     <hyperlink ref="H21" r:id="rId8" xr:uid="{B0FFF7C7-7C5F-48BF-B374-ADD953FC535F}"/>
+    <hyperlink ref="H31" r:id="rId9" xr:uid="{758FB3AE-1CB5-4064-94B5-5BCA666DF382}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId9"/>
+  <pageSetup orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
--- a/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
+++ b/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing\system_development\Damascus\V0.5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1289902ff8f48853/Documents/GitHub/In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing/system_development/Damascus/V0.5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41798B06-F3F8-4A84-B92C-747F8A35EEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{41798B06-F3F8-4A84-B92C-747F8A35EEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09C9265C-CB9E-46A8-AA9C-610611C8A5D7}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21840" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
   <si>
     <t>Total Cost</t>
   </si>
@@ -225,6 +225,18 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/phoenix-contact/2903361/4755334</t>
+  </si>
+  <si>
+    <t>USB-C to USB-A Adapter</t>
+  </si>
+  <si>
+    <t>Eaton Tripp Lite Series USB 3.0 Adapter Converter USB-A to USB Type C M/F USB-C - USB-C adapter - USB A to 24 pin USB-C - U329-000 - USB Adapters - CDWG.com</t>
+  </si>
+  <si>
+    <t>U329-000</t>
+  </si>
+  <si>
+    <t>Eaton Tripp Lite Series USB 3.0 Adapter Converter USB-A to USB Type C M/F USB-C - USB-C adapter - USB A to 24 pin USB-C</t>
   </si>
 </sst>
 </file>
@@ -1255,14 +1267,28 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
+      <c r="A32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="10">
+        <v>13.96</v>
+      </c>
+      <c r="F32" s="10">
+        <v>13.96</v>
+      </c>
       <c r="G32" s="2"/>
-      <c r="H32" s="3"/>
+      <c r="H32" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
@@ -1296,7 +1322,7 @@
       </c>
       <c r="F37" s="5">
         <f>SUM(F2:F36)</f>
-        <v>244.38</v>
+        <v>258.33999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -1311,8 +1337,9 @@
     <hyperlink ref="H20" r:id="rId7" xr:uid="{DFE47E21-CC99-4786-9546-33196C5907C2}"/>
     <hyperlink ref="H21" r:id="rId8" xr:uid="{B0FFF7C7-7C5F-48BF-B374-ADD953FC535F}"/>
     <hyperlink ref="H31" r:id="rId9" xr:uid="{758FB3AE-1CB5-4064-94B5-5BCA666DF382}"/>
+    <hyperlink ref="H32" r:id="rId10" display="https://www.cdwg.com/product/tripp-lite-usb-3.0-adapter-converter-usb-a-to-usb-type-c-m-f-usb-c/5238658?pfm=srh" xr:uid="{3D280BFA-933C-4B78-9942-E3BEECE50362}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
+  <pageSetup orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>
--- a/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
+++ b/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1289902ff8f48853/Documents/GitHub/In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing/system_development/Damascus/V0.5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing\system_development\Damascus\V0.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{41798B06-F3F8-4A84-B92C-747F8A35EEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09C9265C-CB9E-46A8-AA9C-610611C8A5D7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08A0FE1-72F4-417C-BC56-3C6611F1B985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21840" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>Total Cost</t>
   </si>
@@ -74,9 +74,6 @@
     <t>Amount Per Cover</t>
   </si>
   <si>
-    <t>Market Rate</t>
-  </si>
-  <si>
     <t>Internal Part Name</t>
   </si>
   <si>
@@ -237,6 +234,42 @@
   </si>
   <si>
     <t>Eaton Tripp Lite Series USB 3.0 Adapter Converter USB-A to USB Type C M/F USB-C - USB-C adapter - USB A to 24 pin USB-C</t>
+  </si>
+  <si>
+    <t>Light</t>
+  </si>
+  <si>
+    <t>AL143W-625IC</t>
+  </si>
+  <si>
+    <t>2X3 SPOT LIGHT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eBay, need to find a local distirbutor </t>
+  </si>
+  <si>
+    <t>Eathnet hub power sully</t>
+  </si>
+  <si>
+    <t>AC or DC DIN Rail Power Supply 1 Output 48V 1.6A</t>
+  </si>
+  <si>
+    <t>XDR-75E-48</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/mean-well-usa-inc/XDR-75E-48/26080802</t>
+  </si>
+  <si>
+    <t>TRENDnet TI-BG50611 6-Port Industrial 2.5G PoE++ DIN-Rail Switch with 10G Ports</t>
+  </si>
+  <si>
+    <t>2.5G PoE++ DIN-Rail Switch</t>
+  </si>
+  <si>
+    <t>TI-BG50611</t>
+  </si>
+  <si>
+    <t>https://www.newegg.com/trendnet-ti-bg50611/p/0XP-001A-009D1?Item=9SIAHFEKFX4055&amp;_gl=1*1sahfwo*_gcl_au*MTgzODUzMjA1Ni4xNzgyODczNzcy*_ga*OTMxODU5NDQwLjE3ODI4NzM3NzQ.*_ga_TR46GG8HLR*czE3ODI4NzcwNzAkbzIkZzEkdDE3ODI4NzcwNzMkajU3JGwwJGgxNDc0Njg5MTYy</t>
   </si>
 </sst>
 </file>
@@ -314,7 +347,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -343,6 +376,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -686,7 +722,7 @@
     <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="45.5703125" bestFit="1" customWidth="1"/>
@@ -698,10 +734,10 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>10</v>
@@ -738,245 +774,326 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="4"/>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="10">
+        <v>800</v>
+      </c>
+      <c r="F2" s="10">
+        <f>D2*E2</f>
+        <v>800</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="A3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2">
+        <v>6333220</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10">
+        <v>12.7</v>
+      </c>
+      <c r="F3" s="10">
+        <f>D3*E3</f>
+        <v>25.4</v>
+      </c>
       <c r="G3" s="5"/>
-      <c r="H3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="A4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10">
+        <v>73.290000000000006</v>
+      </c>
+      <c r="F4" s="10">
+        <f t="shared" ref="F4" si="0">D4*E4</f>
+        <v>73.290000000000006</v>
+      </c>
+      <c r="G4" s="5"/>
       <c r="H4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="F5" s="10">
+        <f>D5*E5</f>
+        <v>0</v>
+      </c>
       <c r="G5" s="5"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="4"/>
+      <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
+      <c r="F6" s="10">
+        <f>D6*E6</f>
+        <v>0</v>
+      </c>
       <c r="G6" s="5"/>
       <c r="H6" s="1"/>
       <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="4"/>
+      <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+      <c r="F7" s="10">
+        <f>D7*E7</f>
+        <v>0</v>
+      </c>
       <c r="G7" s="5"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2">
-        <v>6333220</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2</v>
-      </c>
-      <c r="E8" s="10">
-        <v>12.7</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="10"/>
       <c r="F8" s="10">
         <f>D8*E8</f>
-        <v>25.4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="H8" s="1"/>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10">
-        <v>73.290000000000006</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="10"/>
       <c r="F9" s="10">
-        <f t="shared" ref="F9:F29" si="0">D9*E9</f>
-        <v>73.290000000000006</v>
+        <f>D9*E9</f>
+        <v>0</v>
       </c>
       <c r="G9" s="5"/>
-      <c r="H9" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="2"/>
+      <c r="A10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+      <c r="F10" s="10">
+        <f>D10*E10</f>
+        <v>0</v>
+      </c>
       <c r="G10" s="5"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
+      <c r="A11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10">
+        <v>4.7</v>
+      </c>
+      <c r="F11" s="10">
+        <f>D11*E11</f>
+        <v>4.7</v>
+      </c>
       <c r="G11" s="5"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="4"/>
+      <c r="H11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="10"/>
+        <v>30</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10">
+        <v>7.58</v>
+      </c>
       <c r="F12" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>D12*E12</f>
+        <v>7.58</v>
       </c>
       <c r="G12" s="5"/>
-      <c r="H12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="10"/>
+        <v>52</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10">
+        <v>1.54</v>
+      </c>
       <c r="F13" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>D13*E13</f>
+        <v>1.54</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="10"/>
+        <v>31</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="10">
+        <v>2.95</v>
+      </c>
       <c r="F14" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>D14*E14</f>
+        <v>2.95</v>
       </c>
       <c r="G14" s="5"/>
-      <c r="H14" s="1"/>
+      <c r="H14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10">
-        <f t="shared" si="0"/>
+        <f>D15*E15</f>
         <v>0</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="1"/>
+      <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10">
-        <f t="shared" si="0"/>
+        <f>D16*E16</f>
         <v>0</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="1"/>
-      <c r="I16" s="3"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10">
-        <f t="shared" si="0"/>
+        <f>D17*E17</f>
         <v>0</v>
       </c>
       <c r="G17" s="5"/>
@@ -985,361 +1102,269 @@
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
-      <c r="E18" s="10">
-        <v>4.7</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="10"/>
       <c r="F18" s="10">
-        <f t="shared" si="0"/>
-        <v>4.7</v>
+        <f>D18*E18</f>
+        <v>0</v>
       </c>
       <c r="G18" s="5"/>
-      <c r="H18" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="H18" s="1"/>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="2">
-        <v>1</v>
-      </c>
-      <c r="E19" s="10">
-        <v>7.58</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="10"/>
       <c r="F19" s="10">
-        <f t="shared" si="0"/>
-        <v>7.58</v>
+        <f>D19*E19</f>
+        <v>0</v>
       </c>
       <c r="G19" s="5"/>
-      <c r="H19" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="H19" s="1"/>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="10">
-        <v>1.54</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="10"/>
       <c r="F20" s="10">
-        <f t="shared" si="0"/>
-        <v>1.54</v>
+        <f>D20*E20</f>
+        <v>0</v>
       </c>
       <c r="G20" s="5"/>
-      <c r="H20" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="H20" s="1"/>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" s="10">
-        <v>2.95</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="10"/>
       <c r="F21" s="10">
-        <f t="shared" si="0"/>
-        <v>2.95</v>
+        <f>D21*E21</f>
+        <v>0</v>
       </c>
       <c r="G21" s="5"/>
-      <c r="H21" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="H21" s="1"/>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="10"/>
+      <c r="E22" s="11"/>
       <c r="F22" s="10">
-        <f t="shared" si="0"/>
+        <f>D22*E22</f>
         <v>0</v>
       </c>
       <c r="G22" s="5"/>
-      <c r="H22" s="1"/>
+      <c r="H22" s="3"/>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="10"/>
+      <c r="A23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="10">
+        <v>110</v>
+      </c>
       <c r="F23" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>D23*E23</f>
+        <v>110</v>
       </c>
       <c r="G23" s="5"/>
-      <c r="H23" s="1"/>
+      <c r="H23" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="10"/>
+      <c r="A24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2903361</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24" s="10">
+        <v>9.4600000000000009</v>
+      </c>
       <c r="F24" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>D24*E24</f>
+        <v>18.920000000000002</v>
       </c>
       <c r="G24" s="5"/>
-      <c r="H24" s="1"/>
+      <c r="H24" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="10"/>
+      <c r="A25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="10">
+        <v>13.96</v>
+      </c>
       <c r="F25" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="1"/>
+        <f>D25*E25</f>
+        <v>13.96</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="10"/>
+      <c r="A26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26" s="10">
+        <v>200</v>
+      </c>
       <c r="F26" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="4"/>
+        <f>D26*E26</f>
+        <v>400</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="10"/>
+      <c r="A27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="10">
+        <v>23</v>
+      </c>
       <c r="F27" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="4"/>
+        <f>D27*E27</f>
+        <v>23</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="4"/>
-    </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="4"/>
-    </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="2">
+      <c r="A28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" s="2">
         <v>1</v>
       </c>
-      <c r="E30" s="10">
-        <v>110</v>
-      </c>
-      <c r="F30" s="10">
-        <f>D30*E30</f>
-        <v>110</v>
-      </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I30" s="4"/>
-    </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="2">
-        <v>2903361</v>
-      </c>
-      <c r="D31" s="2">
-        <v>2</v>
-      </c>
-      <c r="E31" s="10">
-        <v>9.4600000000000009</v>
-      </c>
-      <c r="F31" s="10">
-        <f>D31*E31</f>
-        <v>18.920000000000002</v>
-      </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="2">
-        <v>1</v>
-      </c>
-      <c r="E32" s="10">
-        <v>13.96</v>
-      </c>
-      <c r="F32" s="10">
-        <v>13.96</v>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E28" s="11">
+        <v>329</v>
+      </c>
+      <c r="F28" s="11">
+        <f>D28*E28</f>
+        <v>329</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E37" s="7" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="5">
         <f>SUM(F2:F36)</f>
-        <v>258.33999999999997</v>
+        <v>1810.3400000000001</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H9" r:id="rId1" xr:uid="{CADA28BD-E75E-40BF-91F5-ECEC4DFDD175}"/>
-    <hyperlink ref="H8" r:id="rId2" xr:uid="{0EDC0A57-8E4C-4D3A-8F84-8D905F46C8DF}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{1ECF2406-B0D1-41D2-AB7D-AB233330FD61}"/>
-    <hyperlink ref="H30" r:id="rId4" xr:uid="{09C07DD3-BEB0-4324-912F-D9BB7285A77D}"/>
-    <hyperlink ref="H18" r:id="rId5" xr:uid="{626FADE7-D6F2-4623-B41F-525D88835216}"/>
-    <hyperlink ref="H19" r:id="rId6" xr:uid="{E1235693-0AE4-483A-80C1-C4EB98C7CCE2}"/>
-    <hyperlink ref="H20" r:id="rId7" xr:uid="{DFE47E21-CC99-4786-9546-33196C5907C2}"/>
-    <hyperlink ref="H21" r:id="rId8" xr:uid="{B0FFF7C7-7C5F-48BF-B374-ADD953FC535F}"/>
-    <hyperlink ref="H31" r:id="rId9" xr:uid="{758FB3AE-1CB5-4064-94B5-5BCA666DF382}"/>
-    <hyperlink ref="H32" r:id="rId10" display="https://www.cdwg.com/product/tripp-lite-usb-3.0-adapter-converter-usb-a-to-usb-type-c-m-f-usb-c/5238658?pfm=srh" xr:uid="{3D280BFA-933C-4B78-9942-E3BEECE50362}"/>
+    <hyperlink ref="H4" r:id="rId1" xr:uid="{CADA28BD-E75E-40BF-91F5-ECEC4DFDD175}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{0EDC0A57-8E4C-4D3A-8F84-8D905F46C8DF}"/>
+    <hyperlink ref="H2" r:id="rId3" xr:uid="{1ECF2406-B0D1-41D2-AB7D-AB233330FD61}"/>
+    <hyperlink ref="H23" r:id="rId4" xr:uid="{09C07DD3-BEB0-4324-912F-D9BB7285A77D}"/>
+    <hyperlink ref="H11" r:id="rId5" xr:uid="{626FADE7-D6F2-4623-B41F-525D88835216}"/>
+    <hyperlink ref="H12" r:id="rId6" xr:uid="{E1235693-0AE4-483A-80C1-C4EB98C7CCE2}"/>
+    <hyperlink ref="H13" r:id="rId7" xr:uid="{DFE47E21-CC99-4786-9546-33196C5907C2}"/>
+    <hyperlink ref="H14" r:id="rId8" xr:uid="{B0FFF7C7-7C5F-48BF-B374-ADD953FC535F}"/>
+    <hyperlink ref="H24" r:id="rId9" xr:uid="{758FB3AE-1CB5-4064-94B5-5BCA666DF382}"/>
+    <hyperlink ref="H25" r:id="rId10" display="https://www.cdwg.com/product/tripp-lite-usb-3.0-adapter-converter-usb-a-to-usb-type-c-m-f-usb-c/5238658?pfm=srh" xr:uid="{3D280BFA-933C-4B78-9942-E3BEECE50362}"/>
+    <hyperlink ref="H27" r:id="rId11" xr:uid="{69858AD3-97BB-4924-83ED-505EBD3B921C}"/>
+    <hyperlink ref="H28" r:id="rId12" xr:uid="{E7CDAEAF-246E-429F-942C-8F1434B33468}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId11"/>
+  <pageSetup orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>